--- a/output/yearly_total_coral_cover_iteration_54_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_54_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.274678084521055</v>
+        <v>1.25763494437533</v>
       </c>
       <c r="C3" t="n">
-        <v>4.589736185510185</v>
+        <v>4.620082007048453</v>
       </c>
       <c r="D3" t="n">
-        <v>6.114800943620335</v>
+        <v>6.037939915854852</v>
       </c>
       <c r="E3" t="n">
-        <v>11.97921521365157</v>
+        <v>11.91565686727863</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.429474990503868</v>
+        <v>1.393671760405645</v>
       </c>
       <c r="C4" t="n">
-        <v>5.04510055916623</v>
+        <v>5.133672133804084</v>
       </c>
       <c r="D4" t="n">
-        <v>6.370978530938276</v>
+        <v>6.236195674051961</v>
       </c>
       <c r="E4" t="n">
-        <v>12.84555408060838</v>
+        <v>12.76353956826169</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.634486537423401</v>
+        <v>1.576385425156646</v>
       </c>
       <c r="C5" t="n">
-        <v>5.59008214854973</v>
+        <v>5.812448078980534</v>
       </c>
       <c r="D5" t="n">
-        <v>6.642585948889585</v>
+        <v>6.530132679747417</v>
       </c>
       <c r="E5" t="n">
-        <v>13.86715463486272</v>
+        <v>13.9189661838846</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.858188626241726</v>
+        <v>1.776478227763782</v>
       </c>
       <c r="C6" t="n">
-        <v>6.280525648268773</v>
+        <v>6.635422413346119</v>
       </c>
       <c r="D6" t="n">
-        <v>6.973114021524648</v>
+        <v>6.860955375684631</v>
       </c>
       <c r="E6" t="n">
-        <v>15.11182829603515</v>
+        <v>15.27285601679453</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.114236786881721</v>
+        <v>1.998673886406447</v>
       </c>
       <c r="C7" t="n">
-        <v>7.077686388886689</v>
+        <v>7.571618977667445</v>
       </c>
       <c r="D7" t="n">
-        <v>7.436118547410439</v>
+        <v>7.176775808833583</v>
       </c>
       <c r="E7" t="n">
-        <v>16.62804172317885</v>
+        <v>16.74706867290747</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.319668132599566</v>
+        <v>1.21388129467828</v>
       </c>
       <c r="C8" t="n">
-        <v>4.711569115655433</v>
+        <v>5.228216407225608</v>
       </c>
       <c r="D8" t="n">
-        <v>5.760342992480635</v>
+        <v>5.368016787187267</v>
       </c>
       <c r="E8" t="n">
-        <v>11.79158024073563</v>
+        <v>11.81011448909116</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.675742597400345</v>
+        <v>1.512393867860751</v>
       </c>
       <c r="C9" t="n">
-        <v>5.656073547612781</v>
+        <v>6.459356832479743</v>
       </c>
       <c r="D9" t="n">
-        <v>6.278579898525081</v>
+        <v>5.832578107953793</v>
       </c>
       <c r="E9" t="n">
-        <v>13.61039604353821</v>
+        <v>13.80432880829429</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.05955567405441</v>
+        <v>1.838079995580677</v>
       </c>
       <c r="C10" t="n">
-        <v>6.735983627705685</v>
+        <v>7.947491232099011</v>
       </c>
       <c r="D10" t="n">
-        <v>6.853380626506372</v>
+        <v>6.252783437083649</v>
       </c>
       <c r="E10" t="n">
-        <v>15.64891992826647</v>
+        <v>16.03835466476334</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.448979485217153</v>
+        <v>2.172384957980804</v>
       </c>
       <c r="C11" t="n">
-        <v>7.914523799357534</v>
+        <v>9.575838068182378</v>
       </c>
       <c r="D11" t="n">
-        <v>7.469955087991647</v>
+        <v>6.741620783177568</v>
       </c>
       <c r="E11" t="n">
-        <v>17.83345837256633</v>
+        <v>18.48984380934075</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.859966080452645</v>
+        <v>2.50645754301619</v>
       </c>
       <c r="C12" t="n">
-        <v>9.168892841168701</v>
+        <v>11.27643949793418</v>
       </c>
       <c r="D12" t="n">
-        <v>8.004971397516506</v>
+        <v>7.199632908131727</v>
       </c>
       <c r="E12" t="n">
-        <v>20.03383031913785</v>
+        <v>20.9825299490821</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.264044654811739</v>
+        <v>2.827122113059655</v>
       </c>
       <c r="C13" t="n">
-        <v>10.48578496124185</v>
+        <v>12.9990223052693</v>
       </c>
       <c r="D13" t="n">
-        <v>8.530219813353945</v>
+        <v>7.70625956817673</v>
       </c>
       <c r="E13" t="n">
-        <v>22.28004942940753</v>
+        <v>23.53240398650568</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.886889635131242</v>
+        <v>1.632194828218492</v>
       </c>
       <c r="C14" t="n">
-        <v>7.460281169617428</v>
+        <v>9.04852315311679</v>
       </c>
       <c r="D14" t="n">
-        <v>6.504412334854562</v>
+        <v>5.881670131096725</v>
       </c>
       <c r="E14" t="n">
-        <v>15.85158313960323</v>
+        <v>16.56238811243201</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.956996238691507</v>
+        <v>1.667577015479547</v>
       </c>
       <c r="C15" t="n">
-        <v>7.952441111233397</v>
+        <v>9.822346511081166</v>
       </c>
       <c r="D15" t="n">
-        <v>6.567754696732568</v>
+        <v>5.890928011947774</v>
       </c>
       <c r="E15" t="n">
-        <v>16.47719204665747</v>
+        <v>17.38085153850849</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.309100052819625</v>
+        <v>1.930371240952333</v>
       </c>
       <c r="C16" t="n">
-        <v>9.327869644883178</v>
+        <v>11.62520836020593</v>
       </c>
       <c r="D16" t="n">
-        <v>7.14636734118451</v>
+        <v>6.296429083709875</v>
       </c>
       <c r="E16" t="n">
-        <v>18.78333703888731</v>
+        <v>19.85200868486814</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.87510866268028</v>
+        <v>1.545202164145183</v>
       </c>
       <c r="C17" t="n">
-        <v>8.572090809722855</v>
+        <v>10.72503407270498</v>
       </c>
       <c r="D17" t="n">
-        <v>6.69911253956079</v>
+        <v>5.826319195531291</v>
       </c>
       <c r="E17" t="n">
-        <v>17.14631201196392</v>
+        <v>18.09655543238146</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.16834688446176</v>
+        <v>1.754108258131861</v>
       </c>
       <c r="C18" t="n">
-        <v>9.931978277214411</v>
+        <v>12.55356862429579</v>
       </c>
       <c r="D18" t="n">
-        <v>7.229001045450964</v>
+        <v>6.193689186460447</v>
       </c>
       <c r="E18" t="n">
-        <v>19.32932620712714</v>
+        <v>20.5013660688881</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.205182058325101</v>
+        <v>1.75076049846038</v>
       </c>
       <c r="C19" t="n">
-        <v>10.55384672551546</v>
+        <v>13.44815676735957</v>
       </c>
       <c r="D19" t="n">
-        <v>7.391342845825217</v>
+        <v>6.259505552553154</v>
       </c>
       <c r="E19" t="n">
-        <v>20.15037162966578</v>
+        <v>21.45842281837311</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.482908666379481</v>
+        <v>1.949201161919787</v>
       </c>
       <c r="C20" t="n">
-        <v>12.14430745882643</v>
+        <v>15.44563046389717</v>
       </c>
       <c r="D20" t="n">
-        <v>7.919434753416619</v>
+        <v>6.640816360882615</v>
       </c>
       <c r="E20" t="n">
-        <v>22.54665087862253</v>
+        <v>24.03564798669958</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.490882063669206</v>
+        <v>1.159355681422101</v>
       </c>
       <c r="C21" t="n">
-        <v>8.977454436806362</v>
+        <v>11.30307730348846</v>
       </c>
       <c r="D21" t="n">
-        <v>6.645980353806952</v>
+        <v>5.533591482556019</v>
       </c>
       <c r="E21" t="n">
-        <v>17.11431685428252</v>
+        <v>17.99602446746658</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_54_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_54_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.25763494437533</v>
+        <v>1.276425595434614</v>
       </c>
       <c r="C3" t="n">
-        <v>4.620082007048453</v>
+        <v>4.672242262575087</v>
       </c>
       <c r="D3" t="n">
-        <v>6.037939915854852</v>
+        <v>6.082619253875124</v>
       </c>
       <c r="E3" t="n">
-        <v>11.91565686727863</v>
+        <v>12.03128711188482</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.393671760405645</v>
+        <v>1.43652482713497</v>
       </c>
       <c r="C4" t="n">
-        <v>5.133672133804084</v>
+        <v>5.283255256809014</v>
       </c>
       <c r="D4" t="n">
-        <v>6.236195674051961</v>
+        <v>6.326180332680267</v>
       </c>
       <c r="E4" t="n">
-        <v>12.76353956826169</v>
+        <v>13.04596041662425</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.576385425156646</v>
+        <v>1.648388922757394</v>
       </c>
       <c r="C5" t="n">
-        <v>5.812448078980534</v>
+        <v>6.067423407525833</v>
       </c>
       <c r="D5" t="n">
-        <v>6.530132679747417</v>
+        <v>6.619278918069205</v>
       </c>
       <c r="E5" t="n">
-        <v>13.9189661838846</v>
+        <v>14.33509124835243</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.776478227763782</v>
+        <v>1.885278497224703</v>
       </c>
       <c r="C6" t="n">
-        <v>6.635422413346119</v>
+        <v>7.021054454008665</v>
       </c>
       <c r="D6" t="n">
-        <v>6.860955375684631</v>
+        <v>6.917173162971677</v>
       </c>
       <c r="E6" t="n">
-        <v>15.27285601679453</v>
+        <v>15.82350611420505</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.998673886406447</v>
+        <v>2.155987482742504</v>
       </c>
       <c r="C7" t="n">
-        <v>7.571618977667445</v>
+        <v>8.137956921223152</v>
       </c>
       <c r="D7" t="n">
-        <v>7.176775808833583</v>
+        <v>7.313965031561233</v>
       </c>
       <c r="E7" t="n">
-        <v>16.74706867290747</v>
+        <v>17.60790943552689</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.21388129467828</v>
+        <v>1.367536145657458</v>
       </c>
       <c r="C8" t="n">
-        <v>5.228216407225608</v>
+        <v>5.733558269182688</v>
       </c>
       <c r="D8" t="n">
-        <v>5.368016787187267</v>
+        <v>5.480866034633452</v>
       </c>
       <c r="E8" t="n">
-        <v>11.81011448909116</v>
+        <v>12.5819604494736</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.512393867860751</v>
+        <v>1.74488762862016</v>
       </c>
       <c r="C9" t="n">
-        <v>6.459356832479743</v>
+        <v>7.043061631307675</v>
       </c>
       <c r="D9" t="n">
-        <v>5.832578107953793</v>
+        <v>5.930235676099197</v>
       </c>
       <c r="E9" t="n">
-        <v>13.80432880829429</v>
+        <v>14.71818493602703</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.838079995580677</v>
+        <v>2.133734535117124</v>
       </c>
       <c r="C10" t="n">
-        <v>7.947491232099011</v>
+        <v>8.504008268241593</v>
       </c>
       <c r="D10" t="n">
-        <v>6.252783437083649</v>
+        <v>6.385091829879863</v>
       </c>
       <c r="E10" t="n">
-        <v>16.03835466476334</v>
+        <v>17.02283463323858</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.172384957980804</v>
+        <v>2.521723910972131</v>
       </c>
       <c r="C11" t="n">
-        <v>9.575838068182378</v>
+        <v>10.08427160732122</v>
       </c>
       <c r="D11" t="n">
-        <v>6.741620783177568</v>
+        <v>6.825735298821275</v>
       </c>
       <c r="E11" t="n">
-        <v>18.48984380934075</v>
+        <v>19.43173081711462</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.50645754301619</v>
+        <v>2.889872309115584</v>
       </c>
       <c r="C12" t="n">
-        <v>11.27643949793418</v>
+        <v>11.77997665736471</v>
       </c>
       <c r="D12" t="n">
-        <v>7.199632908131727</v>
+        <v>7.232300682678369</v>
       </c>
       <c r="E12" t="n">
-        <v>20.9825299490821</v>
+        <v>21.90214964915866</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.827122113059655</v>
+        <v>3.230058145152503</v>
       </c>
       <c r="C13" t="n">
-        <v>12.9990223052693</v>
+        <v>13.53998241023367</v>
       </c>
       <c r="D13" t="n">
-        <v>7.70625956817673</v>
+        <v>7.638655167418316</v>
       </c>
       <c r="E13" t="n">
-        <v>23.53240398650568</v>
+        <v>24.40869572280449</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.632194828218492</v>
+        <v>1.843182227338174</v>
       </c>
       <c r="C14" t="n">
-        <v>9.04852315311679</v>
+        <v>9.565933645685984</v>
       </c>
       <c r="D14" t="n">
-        <v>5.881670131096725</v>
+        <v>5.810297072997982</v>
       </c>
       <c r="E14" t="n">
-        <v>16.56238811243201</v>
+        <v>17.21941294602214</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.667577015479547</v>
+        <v>1.874814138369006</v>
       </c>
       <c r="C15" t="n">
-        <v>9.822346511081166</v>
+        <v>10.40909784400132</v>
       </c>
       <c r="D15" t="n">
-        <v>5.890928011947774</v>
+        <v>5.771066434736281</v>
       </c>
       <c r="E15" t="n">
-        <v>17.38085153850849</v>
+        <v>18.0549784171066</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.930371240952333</v>
+        <v>2.156791713982775</v>
       </c>
       <c r="C16" t="n">
-        <v>11.62520836020593</v>
+        <v>12.3618823850416</v>
       </c>
       <c r="D16" t="n">
-        <v>6.296429083709875</v>
+        <v>6.195014545861181</v>
       </c>
       <c r="E16" t="n">
-        <v>19.85200868486814</v>
+        <v>20.71368864488556</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.545202164145183</v>
+        <v>1.713375545882661</v>
       </c>
       <c r="C17" t="n">
-        <v>10.72503407270498</v>
+        <v>11.39764905983856</v>
       </c>
       <c r="D17" t="n">
-        <v>5.826319195531291</v>
+        <v>5.717728081964552</v>
       </c>
       <c r="E17" t="n">
-        <v>18.09655543238146</v>
+        <v>18.82875268768577</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.754108258131861</v>
+        <v>1.935633408647097</v>
       </c>
       <c r="C18" t="n">
-        <v>12.55356862429579</v>
+        <v>13.37976822228174</v>
       </c>
       <c r="D18" t="n">
-        <v>6.193689186460447</v>
+        <v>6.102700809230853</v>
       </c>
       <c r="E18" t="n">
-        <v>20.5013660688881</v>
+        <v>21.41810244015969</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.75076049846038</v>
+        <v>1.923430284683308</v>
       </c>
       <c r="C19" t="n">
-        <v>13.44815676735957</v>
+        <v>14.38542148312696</v>
       </c>
       <c r="D19" t="n">
-        <v>6.259505552553154</v>
+        <v>6.152642314945887</v>
       </c>
       <c r="E19" t="n">
-        <v>21.45842281837311</v>
+        <v>22.46149408275616</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.949201161919787</v>
+        <v>2.125483779694344</v>
       </c>
       <c r="C20" t="n">
-        <v>15.44563046389717</v>
+        <v>16.50331635306748</v>
       </c>
       <c r="D20" t="n">
-        <v>6.640816360882615</v>
+        <v>6.510675885207658</v>
       </c>
       <c r="E20" t="n">
-        <v>24.03564798669958</v>
+        <v>25.13947601796948</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.159355681422101</v>
+        <v>1.255684766162798</v>
       </c>
       <c r="C21" t="n">
-        <v>11.30307730348846</v>
+        <v>12.11915508264362</v>
       </c>
       <c r="D21" t="n">
-        <v>5.533591482556019</v>
+        <v>5.408507007557934</v>
       </c>
       <c r="E21" t="n">
-        <v>17.99602446746658</v>
+        <v>18.78334685636436</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_54_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_54_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.276425595434614</v>
+        <v>2.654448964626055</v>
       </c>
       <c r="C3" t="n">
-        <v>4.672242262575087</v>
+        <v>7.685933048795063</v>
       </c>
       <c r="D3" t="n">
-        <v>6.082619253875124</v>
+        <v>8.217226089603225</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03128711188482</v>
+        <v>18.55760810302434</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.43652482713497</v>
+        <v>1.212766198274369</v>
       </c>
       <c r="C4" t="n">
-        <v>5.283255256809014</v>
+        <v>4.424772896602559</v>
       </c>
       <c r="D4" t="n">
-        <v>6.326180332680267</v>
+        <v>5.836175517432875</v>
       </c>
       <c r="E4" t="n">
-        <v>13.04596041662425</v>
+        <v>11.4737146123098</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.648388922757394</v>
+        <v>1.427152829657428</v>
       </c>
       <c r="C5" t="n">
-        <v>6.067423407525833</v>
+        <v>4.957051252402735</v>
       </c>
       <c r="D5" t="n">
-        <v>6.619278918069205</v>
+        <v>6.222031195709389</v>
       </c>
       <c r="E5" t="n">
-        <v>14.33509124835243</v>
+        <v>12.60623527776955</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.885278497224703</v>
+        <v>1.663210547699752</v>
       </c>
       <c r="C6" t="n">
-        <v>7.021054454008665</v>
+        <v>5.61587772224652</v>
       </c>
       <c r="D6" t="n">
-        <v>6.917173162971677</v>
+        <v>6.678507676412174</v>
       </c>
       <c r="E6" t="n">
-        <v>15.82350611420505</v>
+        <v>13.95759594635845</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.155987482742504</v>
+        <v>1.900046889653962</v>
       </c>
       <c r="C7" t="n">
-        <v>8.137956921223152</v>
+        <v>6.364798637622769</v>
       </c>
       <c r="D7" t="n">
-        <v>7.313965031561233</v>
+        <v>7.147244583273158</v>
       </c>
       <c r="E7" t="n">
-        <v>17.60790943552689</v>
+        <v>15.41209011054989</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.367536145657458</v>
+        <v>2.150594989838043</v>
       </c>
       <c r="C8" t="n">
-        <v>5.733558269182688</v>
+        <v>7.235770444127728</v>
       </c>
       <c r="D8" t="n">
-        <v>5.480866034633452</v>
+        <v>7.651726406651342</v>
       </c>
       <c r="E8" t="n">
-        <v>12.5819604494736</v>
+        <v>17.03809184061711</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.74488762862016</v>
+        <v>2.395943138640973</v>
       </c>
       <c r="C9" t="n">
-        <v>7.043061631307675</v>
+        <v>8.265971090131382</v>
       </c>
       <c r="D9" t="n">
-        <v>5.930235676099197</v>
+        <v>8.135103412508956</v>
       </c>
       <c r="E9" t="n">
-        <v>14.71818493602703</v>
+        <v>18.79701764128131</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.133734535117124</v>
+        <v>1.428825791283765</v>
       </c>
       <c r="C10" t="n">
-        <v>8.504008268241593</v>
+        <v>6.260526570165569</v>
       </c>
       <c r="D10" t="n">
-        <v>6.385091829879863</v>
+        <v>6.434060294368236</v>
       </c>
       <c r="E10" t="n">
-        <v>17.02283463323858</v>
+        <v>14.12341265581757</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.521723910972131</v>
+        <v>1.414875156406418</v>
       </c>
       <c r="C11" t="n">
-        <v>10.08427160732122</v>
+        <v>6.56219800472653</v>
       </c>
       <c r="D11" t="n">
-        <v>6.825735298821275</v>
+        <v>6.369196223548649</v>
       </c>
       <c r="E11" t="n">
-        <v>19.43173081711462</v>
+        <v>14.3462693846816</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.889872309115584</v>
+        <v>1.598275445036765</v>
       </c>
       <c r="C12" t="n">
-        <v>11.77997665736471</v>
+        <v>7.729319310489224</v>
       </c>
       <c r="D12" t="n">
-        <v>7.232300682678369</v>
+        <v>6.880009371545309</v>
       </c>
       <c r="E12" t="n">
-        <v>21.90214964915866</v>
+        <v>16.2076041270713</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.230058145152503</v>
+        <v>1.291587279707104</v>
       </c>
       <c r="C13" t="n">
-        <v>13.53998241023367</v>
+        <v>7.362872162402059</v>
       </c>
       <c r="D13" t="n">
-        <v>7.638655167418316</v>
+        <v>6.370482313041212</v>
       </c>
       <c r="E13" t="n">
-        <v>24.40869572280449</v>
+        <v>15.02494175515038</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.843182227338174</v>
+        <v>1.441961575566588</v>
       </c>
       <c r="C14" t="n">
-        <v>9.565933645685984</v>
+        <v>8.597223550951574</v>
       </c>
       <c r="D14" t="n">
-        <v>5.810297072997982</v>
+        <v>6.82882104624588</v>
       </c>
       <c r="E14" t="n">
-        <v>17.21941294602214</v>
+        <v>16.86800617276404</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.874814138369006</v>
+        <v>1.431898661598058</v>
       </c>
       <c r="C15" t="n">
-        <v>10.40909784400132</v>
+        <v>9.264281846079111</v>
       </c>
       <c r="D15" t="n">
-        <v>5.771066434736281</v>
+        <v>6.967993600799906</v>
       </c>
       <c r="E15" t="n">
-        <v>18.0549784171066</v>
+        <v>17.66417410847707</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.156791713982775</v>
+        <v>1.583951746031804</v>
       </c>
       <c r="C16" t="n">
-        <v>12.3618823850416</v>
+        <v>10.80206199758019</v>
       </c>
       <c r="D16" t="n">
-        <v>6.195014545861181</v>
+        <v>7.442590075986899</v>
       </c>
       <c r="E16" t="n">
-        <v>20.71368864488556</v>
+        <v>19.82860381959889</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.713375545882661</v>
+        <v>0.9428901301127218</v>
       </c>
       <c r="C17" t="n">
-        <v>11.39764905983856</v>
+        <v>8.144431692275903</v>
       </c>
       <c r="D17" t="n">
-        <v>5.717728081964552</v>
+        <v>6.241068330667398</v>
       </c>
       <c r="E17" t="n">
-        <v>18.82875268768577</v>
+        <v>15.32839015305602</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.935633408647097</v>
+        <v>0.7623369098246909</v>
       </c>
       <c r="C18" t="n">
-        <v>13.37976822228174</v>
+        <v>7.187836364211896</v>
       </c>
       <c r="D18" t="n">
-        <v>6.102700809230853</v>
+        <v>5.762377967553696</v>
       </c>
       <c r="E18" t="n">
-        <v>21.41810244015969</v>
+        <v>13.71255124159028</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.923430284683308</v>
+        <v>0.8968167103524188</v>
       </c>
       <c r="C19" t="n">
-        <v>14.38542148312696</v>
+        <v>8.848914209889328</v>
       </c>
       <c r="D19" t="n">
-        <v>6.152642314945887</v>
+        <v>6.331732731154591</v>
       </c>
       <c r="E19" t="n">
-        <v>22.46149408275616</v>
+        <v>16.07746365139634</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.125483779694344</v>
+        <v>1.02971589707631</v>
       </c>
       <c r="C20" t="n">
-        <v>16.50331635306748</v>
+        <v>10.60785266672608</v>
       </c>
       <c r="D20" t="n">
-        <v>6.510675885207658</v>
+        <v>6.93729435008811</v>
       </c>
       <c r="E20" t="n">
-        <v>25.13947601796948</v>
+        <v>18.5748629138905</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.255684766162798</v>
+        <v>1.155212706110179</v>
       </c>
       <c r="C21" t="n">
-        <v>12.11915508264362</v>
+        <v>12.38188058577711</v>
       </c>
       <c r="D21" t="n">
-        <v>5.408507007557934</v>
+        <v>7.463844913783842</v>
       </c>
       <c r="E21" t="n">
-        <v>18.78334685636436</v>
+        <v>21.00093820567113</v>
       </c>
     </row>
   </sheetData>
